--- a/PlantillaSemanal_Exportada.xlsx
+++ b/PlantillaSemanal_Exportada.xlsx
@@ -614,7 +614,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>LUNES 3 DE MARZO 2025</t>
+          <t>LUNES 20 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -675,12 +675,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>SOTO VELAZCO, EMIR ALESSANDRO</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>06:30-10:15</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -689,28 +689,20 @@
           <t>1 PREF</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>(T) HUAMANI HUAMAN, MARICRUZ DESIDE</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>21:45-22:45</t>
-        </is>
-      </c>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>JIMENEZ VERGARA, ADRIAN MARCELO</t>
+          <t>(T) HUAMANI PONCE, ELVIS BENITO</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10:00-13:45</t>
+          <t>15:45-22:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -723,12 +715,12 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) TITO LAURA, NANCY FIORELLA</t>
+          <t>(T) CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>13:30-22:00</t>
+          <t>21:45-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -743,12 +735,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA RICALDE, LILIA MARIA</t>
+          <t>TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>08:00-17:00</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -763,12 +755,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>POVEA CANTARO, FARID YASSER</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>17:00-20:45</t>
+          <t>13:00-22:00</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -783,40 +775,32 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:15-12:00</t>
+          <t>08:30-13:00</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>SUICA GOÑAS, KEISY YVONNE</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>15:45-19:30</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>LOPEZ SANCHEZ, NELLY ANDREA</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>12:00-15:45</t>
+          <t>13:00-22:00</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -831,54 +815,38 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>09:15-13:00</t>
+          <t>09:45-14:15</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI LOPEZ, DREYDI BELINDA</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>14:15-18:00</t>
-        </is>
-      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>TITO LAURA, NANCY FIORELLA</t>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>13:00-13:30</t>
+          <t>16:00-20:30</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="14" t="n"/>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>RAMOS FARFAN, BRYAN  ENRIQUE</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
@@ -887,40 +855,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ALVITE CORNEJO, ANGIE LUCERO</t>
+          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>09:45-13:30</t>
+          <t>10:00-14:30</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MAYTA QUINTANA, ANDY KEVIN</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ZAPATA VILLANUEVA, FIORELLA YASMIN</t>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>14:15-18:00</t>
+          <t>17:00-21:30</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -935,40 +895,32 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CASAPAICO RIVERA, ENZO MANUEL</t>
+          <t>HUAMANI PONCE, ELVIS BENITO</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>10:30-14:15</t>
+          <t>13:00-15:45</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI HUAMAN, MARICRUZ DESIDE</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>19:00-21:45</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>MUÑOZ SOTOMAYOR, MIRIAN RAQUEL</t>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>15:00-18:45</t>
+          <t>17:00-21:30</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -983,12 +935,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CUSI QUISPE, ANDREA ESTEFANY</t>
+          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>10:30-14:15</t>
+          <t>17:15-21:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -1001,16 +953,8 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>HUANCAS SHUAN, JOSELYN JAZMIN</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>16:15-20:00</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1023,12 +967,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>BRANCACHO RAMIREZ, BRINDY</t>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>18:15-21:45</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -1041,16 +985,8 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="14" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>BARRIENTOS JERI, MILAGROS NICOL</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>17:00-22:00</t>
-        </is>
-      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -1063,12 +999,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA MALLQUI, CYNTHIA ANGELLINE</t>
+          <t>BENAVIDES PEZO, JAIME EMILIO</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>11:15-15:00</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -1081,16 +1017,8 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="14" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>LA ROSA EUSEBIO, SHADIA SHAMIRA</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>17:15-21:00</t>
-        </is>
-      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -1103,12 +1031,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>PEREZ GORMAS, ANTHONY</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>18:00-21:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
@@ -1133,16 +1061,8 @@
       <c r="A25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>SALVATIERRA PAREJA, MARCO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="14" t="n">
         <v>11</v>
@@ -1165,16 +1085,8 @@
       <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>ALARCON SANDOVAL, ADRIANA FERNANDA</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="14" t="n">
         <v>12</v>
@@ -1197,16 +1109,8 @@
       <c r="A29" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>LEON TICONA, MARIA FERNANDA</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="14" t="n">
         <v>13</v>
@@ -1394,7 +1298,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>09:30-18:30</t>
+          <t>10:00-19:00</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -1407,16 +1311,8 @@
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="14" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="14" t="n"/>
       <c r="F45" s="3" t="n"/>
@@ -1429,12 +1325,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>QUISPE MONDRAGON, JUAN ALFONSO</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
@@ -1443,12 +1339,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>YANQUI BRAVO, MIRIAN LUZ</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>15:00-18:45</t>
+          <t>16:00-20:30</t>
         </is>
       </c>
       <c r="H46" s="3" t="n"/>
@@ -1457,34 +1353,34 @@
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>IDME GOMEZ, MILAGROS</t>
+          <t>CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:30-16:00</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="14" t="n"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>VILCAPOMA CHILIN, JULISSA JAZMIN</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>18:45-22:30</t>
-        </is>
-      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>BENAVIDES PEZO, JAIME EMILIO</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>18:15-22:45</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="14" t="n">
         <v>23</v>
@@ -1549,12 +1445,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HUANUCO VICUÑA, ABIGAIL LUZ</t>
+          <t>QUISPE VERA, STEFANI XIOMARA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
@@ -1563,16 +1459,8 @@
           <t>25-30</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>MACHCO HUARCA, NICOLAS AXEL</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
@@ -1583,12 +1471,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>ZARATE ALAGON, FEDERICO ALEXANDER</t>
+          <t>SELF, MARIANA</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:00-15:30</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -1609,12 +1497,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CARHUANCHO RAYMUNDO, JAMES JESUS</t>
+          <t>SELF, ERIKA</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>14:00-23:00</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
@@ -1675,7 +1563,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>MARTES 4 DE MARZO 2025</t>
+          <t>MARTES 21 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -1736,12 +1624,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>SOTO VELAZCO, EMIR ALESSANDRO</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -1750,54 +1638,38 @@
           <t>1 PREF</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>(T) PEREZ GORMAS, ANTHONY</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>17:30-20:45</t>
-        </is>
-      </c>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>QUIQUIA MALLQUI, CYNTHIA ANGELLINE</t>
+          <t>(T) JANAMPA CIRIACO, GIAN BRAYAN</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10:30-14:15</t>
+          <t>15:45-20:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>(T) ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>20:30-22:45</t>
-        </is>
-      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>ZAPATA VILLANUEVA, FIORELLA YASMIN</t>
+          <t>(T) LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>14:00-17:45</t>
+          <t>19:45-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -1812,12 +1684,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA RICALDE, LILIA MARIA</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>08:00-17:00</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -1832,12 +1704,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>BONILLA SANCHEZ, RAUL FERNANDO</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>17:00-20:45</t>
+          <t>12:15-21:15</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -1852,42 +1724,26 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CUSI QUISPE, ANDREA ESTEFANY</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:15-12:00</t>
+          <t>09:30-18:30</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>VILCAPOMA CHILIN, JULISSA JAZMIN</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>18:30-22:15</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI LOPEZ, DREYDI BELINDA</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>14:45-18:30</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -1900,12 +1756,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CASAPAICO RIVERA, ENZO MANUEL</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>09:00-12:45</t>
+          <t>10:00-14:30</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -1914,12 +1770,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>19:00-20:30</t>
+          <t>17:00-21:30</t>
         </is>
       </c>
       <c r="H11" s="3" t="n"/>
@@ -1928,12 +1784,12 @@
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>SUICA GOÑAS, KEISY YVONNE</t>
+          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>15:15-19:00</t>
+          <t>15:30-15:45</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -1948,40 +1804,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10:15-14:00</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>HUANCAS SHUAN, JOSELYN JAZMIN</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ALARCON SANDOVAL, ADRIANA FERNANDA</t>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>15:15-19:00</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -1996,12 +1844,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>MUÑOZ SOTOMAYOR, MIRIAN RAQUEL</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>13:45-19:45</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -2014,16 +1862,8 @@
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>LA ROSA EUSEBIO, SHADIA SHAMIRA</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>15:30-19:15</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -2036,42 +1876,26 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>BRANCACHO RAMIREZ, BRINDY</t>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>17:45-22:15</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>FABIAN VALDIVIA, LINDSAY ZIYI</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>PEREZ GORMAS, ANTHONY</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>17:00-17:30</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -2084,12 +1908,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>YANQUI BRAVO, MIRIAN LUZ</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11:30-15:15</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -2102,16 +1926,8 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="14" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>POVEA CANTARO, FARID YASSER</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -2124,12 +1940,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>ALVITE CORNEJO, ANGIE LUCERO</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>11:45-15:30</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -2142,16 +1958,8 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="14" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>SALVATIERRA PAREJA, MARCO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -2162,16 +1970,8 @@
       <c r="A23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>MAYTA QUINTANA, ANDY KEVIN</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -2431,7 +2231,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>09:30-18:30</t>
+          <t>09:00-18:00</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -2446,12 +2246,12 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>SICHA JORGE, JOSE ANGELO</t>
+          <t>BENAVIDES PEZO, JAIME EMILIO</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>19:00-22:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
@@ -2466,12 +2266,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>QUISPE MONDRAGON, JUAN ALFONSO</t>
+          <t>ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
@@ -2480,12 +2280,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>RAMOS FARFAN, BRYAN  ENRIQUE</t>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>16:00-20:30</t>
         </is>
       </c>
       <c r="H46" s="3" t="n"/>
@@ -2494,26 +2294,18 @@
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:30-16:00</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="14" t="n"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI HUAMAN, MARICRUZ DESIDE</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
@@ -2586,12 +2378,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HUANUCO VICUÑA, ABIGAIL LUZ</t>
+          <t>RAMIREZ COTERA, PILAR SINTYA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
@@ -2600,8 +2392,16 @@
           <t>25-30</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>SELF, MARIANA</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>18:00-22:30</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
@@ -2612,12 +2412,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CARHUANCHO RAYMUNDO, JAMES JESUS</t>
+          <t>ALVITES MOZOMBITE, DANIEL ANDRES</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>11:00-15:30</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -2638,12 +2438,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>ZARATE ALAGON, FEDERICO ALEXANDER</t>
+          <t>SELF, ERIKA</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>19:15-23:00</t>
+          <t>14:00-23:00</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
@@ -2704,7 +2504,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>MIÉRCOLES 5 DE MARZO 2025</t>
+          <t>MIÉRCOLES 22 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -2765,12 +2565,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>SOTO VELAZCO, EMIR ALESSANDRO</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>06:30-10:15</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -2779,68 +2579,44 @@
           <t>1 PREF</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>(T) SICHA JORGE, JOSE ANGELO</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>15:15-18:45</t>
-        </is>
-      </c>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>(T) ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10:00-13:45</t>
+          <t>15:45-18:30</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>HUANCAS SHUAN, JOSELYN JAZMIN</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>18:30-22:15</t>
-        </is>
-      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) IDME GOMEZ, MILAGROS</t>
+          <t>(T) LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>13:30-15:30</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="9" t="n"/>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>(T) TITO LAURA, NANCY FIORELLA</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>22:00-22:45</t>
-        </is>
-      </c>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
       <c r="H6" s="10" t="n"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
@@ -2849,12 +2625,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>JIMENEZ VERGARA, ADRIAN MARCELO</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>08:00-11:45</t>
+          <t>08:00-12:30</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -2863,12 +2639,12 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>TITO LAURA, NANCY FIORELLA</t>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>13:45-22:00</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="H7" s="3" t="n"/>
@@ -2877,12 +2653,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>IDME GOMEZ, MILAGROS</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>11:45-13:30</t>
+          <t>13:45-18:15</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -2897,42 +2673,26 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>QUISPE MONDRAGON, JUAN ALFONSO</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:15-12:00</t>
+          <t>10:00-19:00</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>FABIAN VALDIVIA, LINDSAY ZIYI</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>17:45-21:30</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>ZAPATA VILLANUEVA, FIORELLA YASMIN</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>14:00-17:45</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -2945,12 +2705,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA RICALDE, LILIA MARIA</t>
+          <t>ALMENDRE ALMENDRE, KATHERINE</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10:00-19:00</t>
+          <t>10:00-14:30</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -2965,12 +2725,12 @@
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>SALVATIERRA PAREJA, MARCO ANTONIO</t>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>19:00-22:45</t>
+          <t>16:00-20:30</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -2985,40 +2745,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10:00-13:45</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MAYTA QUINTANA, ANDY KEVIN</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>LA ROSA EUSEBIO, SHADIA SHAMIRA</t>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>14:15-18:00</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -3033,40 +2785,32 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CUSI QUISPE, ANDREA ESTEFANY</t>
+          <t>TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>10:15-14:00</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>SUICA GOÑAS, KEISY YVONNE</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>15:30-19:15</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>SICHA JORGE, JOSE ANGELO</t>
+          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>15:00-15:15</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -3081,12 +2825,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ALVITE CORNEJO, ANGIE LUCERO</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>10:30-14:15</t>
+          <t>14:00-15:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -3101,12 +2845,12 @@
       <c r="A18" s="14" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>MUÑOZ SOTOMAYOR, MIRIAN RAQUEL</t>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>16:00-19:45</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
@@ -3121,12 +2865,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>HUAMANI HUAMAN, MARICRUZ DESIDE</t>
+          <t>BENAVIDES PEZO, JAIME EMILIO</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -3139,16 +2883,8 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="14" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>BONILLA SANCHEZ, RAUL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>17:00-20:45</t>
-        </is>
-      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -3159,16 +2895,8 @@
       <c r="A21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>LEON TICONA, MARIA FERNANDA</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="14" t="n">
         <v>9</v>
@@ -3191,16 +2919,8 @@
       <c r="A23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>PEREZ GORMAS, ANTHONY</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -3223,16 +2943,8 @@
       <c r="A25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>POVEA CANTARO, FARID YASSER</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>18:45-22:30</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="14" t="n">
         <v>11</v>
@@ -3468,7 +3180,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>09:15-18:15</t>
+          <t>09:00-18:00</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -3483,12 +3195,12 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>19:00-22:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
@@ -3503,54 +3215,38 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CASAPAICO RIVERA, ENZO MANUEL</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI LOPEZ, DREYDI BELINDA</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>14:30-18:15</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA MALLQUI, CYNTHIA ANGELLINE</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>13:30-22:30</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="14" t="n"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>RAMOS FARFAN, BRYAN  ENRIQUE</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
@@ -3623,12 +3319,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HUANUCO VICUÑA, ABIGAIL LUZ</t>
+          <t>RAMIREZ COTERA, PILAR SINTYA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
@@ -3639,12 +3335,12 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>MACHCO HUARCA, NICOLAS AXEL</t>
+          <t>ZUNIGA ANDRADE, JUAN ANTONIO</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>18:15-22:00</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="H53" s="8" t="n"/>
@@ -3657,12 +3353,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>ZARATE ALAGON, FEDERICO ALEXANDER</t>
+          <t>ALVITES MOZOMBITE, DANIEL ANDRES</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:00-15:30</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -3683,12 +3379,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CARHUANCHO RAYMUNDO, JAMES JESUS</t>
+          <t>SELF, ERIKA</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>14:00-23:00</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
@@ -3749,7 +3445,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>JUEVES 6 DE MARZO 2025</t>
+          <t>JUEVES 23 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -3810,12 +3506,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>SOTO VELAZCO, EMIR ALESSANDRO</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>06:30-10:15</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -3824,54 +3520,38 @@
           <t>1 PREF</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>(T) HUANCAS SHUAN, JOSELYN JAZMIN</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>16:30-19:45</t>
-        </is>
-      </c>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10:00-13:45</t>
+          <t>15:45-20:15</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>(T) TITO LAURA, NANCY FIORELLA</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>19:30-22:45</t>
-        </is>
-      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) ALVITE CORNEJO, ANGIE LUCERO</t>
+          <t>(T) LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>13:30-16:45</t>
+          <t>20:00-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -3886,12 +3566,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA RICALDE, LILIA MARIA</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>08:00-17:00</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -3906,12 +3586,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>LA ROSA EUSEBIO, SHADIA SHAMIRA</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>17:00-20:45</t>
+          <t>13:00-22:00</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -3926,40 +3606,32 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>JIMENEZ VERGARA, ADRIAN MARCELO</t>
+          <t>TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:15-12:00</t>
+          <t>09:45-14:15</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>TITO LAURA, NANCY FIORELLA</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>13:45-19:30</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ALVITE CORNEJO, ANGIE LUCERO</t>
+          <t>BENAVIDES PEZO, JAIME EMILIO</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>13:00-13:30</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -3974,42 +3646,26 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>SUICA GOÑAS, KEISY YVONNE</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10:00-13:45</t>
+          <t>10:00-19:00</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>PEREZ GORMAS, ANTHONY</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ZAPATA VILLANUEVA, FIORELLA YASMIN</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>14:15-18:00</t>
-        </is>
-      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -4022,40 +3678,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>ALMENDRE ALMENDRE, KATHERINE</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10:15-14:00</t>
+          <t>10:00-14:30</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>FABIAN VALDIVIA, LINDSAY ZIYI</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>YANQUI BRAVO, MIRIAN LUZ</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>15:15-19:00</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -4070,42 +3718,26 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA MALLQUI, CYNTHIA ANGELLINE</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>10:30-14:15</t>
+          <t>13:45-20:00</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>SICHA JORGE, JOSE ANGELO</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>16:45-20:30</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>HUANCAS SHUAN, JOSELYN JAZMIN</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>16:00-16:30</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -4118,12 +3750,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CASAPAICO RIVERA, ENZO MANUEL</t>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -4136,16 +3768,8 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>ALARCON SANDOVAL, ADRIANA FERNANDA</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>17:45-21:30</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -4156,16 +3780,8 @@
       <c r="A19" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>BRANCACHO RAMIREZ, BRINDY</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>11:15-15:00</t>
-        </is>
-      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="14" t="n">
         <v>8</v>
@@ -4176,16 +3792,8 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="14" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>POVEA CANTARO, FARID YASSER</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>17:45-21:30</t>
-        </is>
-      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -4196,16 +3804,8 @@
       <c r="A21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>RAMOS FARFAN, BRYAN  ENRIQUE</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="14" t="n">
         <v>9</v>
@@ -4228,16 +3828,8 @@
       <c r="A23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>BONILLA SANCHEZ, RAUL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -4260,16 +3852,8 @@
       <c r="A25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>VILCAPOMA CHILIN, JULISSA JAZMIN</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>18:30-22:15</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="14" t="n">
         <v>11</v>
@@ -4505,7 +4089,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>09:30-18:30</t>
+          <t>09:00-18:00</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -4520,12 +4104,12 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>19:00-22:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
@@ -4540,12 +4124,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>QUISPE MONDRAGON, JUAN ALFONSO</t>
+          <t>ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
@@ -4554,12 +4138,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>LEON TICONA, MARIA FERNANDA</t>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>17:00-21:30</t>
         </is>
       </c>
       <c r="H46" s="3" t="n"/>
@@ -4568,26 +4152,18 @@
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>IDME GOMEZ, MILAGROS</t>
+          <t>CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:30-16:00</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="14" t="n"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI HUAMAN, MARICRUZ DESIDE</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
@@ -4660,12 +4236,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HUANUCO VICUÑA, ABIGAIL LUZ</t>
+          <t>RAMIREZ COTERA, PILAR SINTYA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
@@ -4674,8 +4250,16 @@
           <t>25-30</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>ZUNIGA ANDRADE, JUAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>18:00-22:30</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
@@ -4686,12 +4270,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MACHCO HUARCA, NICOLAS AXEL</t>
+          <t>QUISPE VERA, STEFANI XIOMARA</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:00-15:30</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -4712,12 +4296,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CARHUANCHO RAYMUNDO, JAMES JESUS</t>
+          <t>SELF, LIZBET</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>14:00-23:00</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
@@ -4778,7 +4362,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>VIERNES 7 DE MARZO 2025</t>
+          <t>VIERNES 24 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -4839,12 +4423,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>CASAPAICO RIVERA, ENZO MANUEL</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -4861,12 +4445,12 @@
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>QUIQUIA MALLQUI, CYNTHIA ANGELLINE</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10:30-14:15</t>
+          <t>11:15-20:15</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -4879,12 +4463,12 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) TITO LAURA, NANCY FIORELLA</t>
+          <t>(T) LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>14:00-22:45</t>
+          <t>20:00-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -4899,54 +4483,38 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>JIMENEZ VERGARA, ADRIAN MARCELO</t>
+          <t>CARBAJAL AGUIRRE, ANGELI ESTRELLA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>07:45-11:30</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>PEREZ GORMAS, ANTHONY</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>15:15-19:00</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>YANQUI BRAVO, MIRIAN LUZ</t>
+          <t>BENAVIDES PEZO, JAIME EMILIO</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>11:30-15:15</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="14" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>FABIAN VALDIVIA, LINDSAY ZIYI</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
@@ -4955,54 +4523,38 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CUSI QUISPE, ANDREA ESTEFANY</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:15-12:00</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>ZAPATA VILLANUEVA, FIORELLA YASMIN</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>14:15-18:00</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TITO LAURA, NANCY FIORELLA</t>
+          <t>URBANO ARCOS, FLOR DELIZ</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>13:45-14:00</t>
+          <t>12:15-21:00</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="14" t="n"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>POVEA CANTARO, FARID YASSER</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
@@ -5011,40 +4563,32 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IDME GOMEZ, MILAGROS</t>
+          <t>HUAMANI PONCE, ELVIS BENITO</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>09:15-13:00</t>
+          <t>09:30-18:30</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>VILCAPOMA CHILIN, JULISSA JAZMIN</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>HUAMANI LOPEZ, DREYDI BELINDA</t>
+          <t>ROMERO HANARI, VENUS ANUSKA</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>18:30-22:15</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -5059,40 +4603,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>HUARACA HUAMAN, DIEGO ADRIEL</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>09:45-13:30</t>
+          <t>10:00-14:00</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>LEON TICONA, MARIA FERNANDA</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>HUANCAS SHUAN, JOSELYN JAZMIN</t>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>15:15-19:00</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -5107,12 +4643,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>RAMOS TINOCO, JORDAN JAVIER</t>
+          <t>ALMENDRE ALMENDRE, KATHERINE</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>10:00-18:45</t>
+          <t>10:15-14:45</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -5127,12 +4663,12 @@
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ALARCON SANDOVAL, ADRIANA FERNANDA</t>
+          <t>CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>18:45-22:30</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -5147,12 +4683,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ALVITE CORNEJO, ANGIE LUCERO</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>13:00-22:00</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -5165,16 +4701,8 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>BONILLA SANCHEZ, RAUL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>16:30-20:15</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -5187,12 +4715,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>BRANCACHO RAMIREZ, BRINDY</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>13:45-20:00</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -5205,16 +4733,8 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="14" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>SICHA JORGE, JOSE ANGELO</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>17:00-20:45</t>
-        </is>
-      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -5225,16 +4745,8 @@
       <c r="A21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>MUÑOZ SOTOMAYOR, MIRIAN RAQUEL</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>11:30-15:15</t>
-        </is>
-      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="14" t="n">
         <v>9</v>
@@ -5245,16 +4757,8 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="14" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ROA ZARATE, ELIZABETH LUCY</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -5265,16 +4769,8 @@
       <c r="A23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>MAYTA QUINTANA, ANDY KEVIN</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -5297,16 +4793,8 @@
       <c r="A25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>ROMERO HAÑARI, VENUS ANUSKA</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>18:30-22:00</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="14" t="n">
         <v>11</v>
@@ -5542,7 +5030,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>10:00-19:00</t>
+          <t>09:00-18:00</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -5557,12 +5045,12 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>SALVATIERRA PAREJA, MARCO ANTONIO</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>19:00-22:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
@@ -5577,12 +5065,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>QUISPE MONDRAGON, JUAN ALFONSO</t>
+          <t>NAVARRO CASTILLO, LIZ MARIELA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
@@ -5597,12 +5085,12 @@
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA RICALDE, LILIA MARIA</t>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10:45-19:45</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -5681,12 +5169,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>ZARATE ALAGON, FEDERICO ALEXANDER</t>
+          <t>ALVITES MOZOMBITE, DANIEL ANDRES</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
@@ -5695,8 +5183,16 @@
           <t>25-30</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>ZUNIGA ANDRADE, JUAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>18:00-22:30</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
@@ -5707,12 +5203,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CARHUANCHO RAYMUNDO, JAMES JESUS</t>
+          <t>QUISPE VERA, STEFANI XIOMARA</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>11:30-16:00</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -5733,12 +5229,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>MACHCO HUARCA, NICOLAS AXEL</t>
+          <t>SELF, ERIKA</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>18:15-22:00</t>
+          <t>14:00-23:00</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
@@ -5799,7 +5295,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>SÁBADO 8 DE MARZO 2025</t>
+          <t>SÁBADO 25 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -5860,12 +5356,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>SOTO VELAZCO, EMIR ALESSANDRO</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>06:30-10:15</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -5874,28 +5370,20 @@
           <t>1 PREF</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>(T) ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>22:15-22:45</t>
-        </is>
-      </c>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>RAMOS TINOCO, JORDAN JAVIER</t>
+          <t>(T) CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>10:00-19:00</t>
+          <t>12:00-15:30</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -5908,12 +5396,12 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>VILCAPOMA CHILIN, JULISSA JAZMIN</t>
+          <t>(T) ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>18:45-22:30</t>
+          <t>15:15-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -5933,49 +5421,33 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>07:45-11:30</t>
+          <t>09:30-14:00</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>FABIAN VALDIVIA, LINDSAY ZIYI</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>15:15-19:00</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>YANQUI BRAVO, MIRIAN LUZ</t>
+          <t>URBANO ARCOS, FLOR DELIZ</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>11:30-15:15</t>
+          <t>15:45-22:30</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="14" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:15</t>
-        </is>
-      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
@@ -5984,42 +5456,26 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:00-11:45</t>
+          <t>10:00-19:00</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>PEREZ GORMAS, ANTHONY</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>17:15-21:00</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>IDME GOMEZ, MILAGROS</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>12:00-15:45</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -6032,12 +5488,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>BARRIENTOS JERI, MILAGROS NICOL</t>
+          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>08:45-17:45</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -6052,12 +5508,12 @@
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>SUICA GOÑAS, KEISY YVONNE</t>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>17:45-21:30</t>
+          <t>16:15-20:45</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -6072,42 +5528,26 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CUSI QUISPE, ANDREA ESTEFANY</t>
+          <t>ROMERO HANARI, VENUS ANUSKA</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>09:30-13:15</t>
+          <t>10:30-19:15</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>BONILLA SANCHEZ, RAUL FERNANDO</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI LOPEZ, DREYDI BELINDA</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>13:30-17:15</t>
-        </is>
-      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -6120,40 +5560,32 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>JIMENEZ VERGARA, ADRIAN MARCELO</t>
+          <t>CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>09:45-13:30</t>
+          <t>11:00-12:00</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>SICHA JORGE, JOSE ANGELO</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ALARCON SANDOVAL, ADRIANA FERNANDA</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>15:15-19:00</t>
+          <t>12:45-21:45</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -6168,12 +5600,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>HUAMANI HUAMAN, MARICRUZ DESIDE</t>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>10:00-13:45</t>
+          <t>17:15-21:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -6186,16 +5618,8 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>HUANCAS SHUAN, JOSELYN JAZMIN</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -6208,12 +5632,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ROMERO HAÑARI, VENUS ANUSKA</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>10:15-19:15</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -6240,12 +5664,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA MALLQUI, CYNTHIA ANGELLINE</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>10:30-14:15</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -6258,16 +5682,8 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="14" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>LA ROSA EUSEBIO, SHADIA SHAMIRA</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -6280,12 +5696,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>BRANCACHO RAMIREZ, BRINDY</t>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
@@ -6298,16 +5714,8 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="14" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>MAYTA QUINTANA, ANDY KEVIN</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="3" t="n"/>
@@ -6318,16 +5726,8 @@
       <c r="A25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>ROA ZARATE, ELIZABETH LUCY</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>11:00-19:45</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="14" t="n">
         <v>11</v>
@@ -6350,16 +5750,8 @@
       <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>MUÑOZ SOTOMAYOR, MIRIAN RAQUEL</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>11:15-15:00</t>
-        </is>
-      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="14" t="n">
         <v>12</v>
@@ -6370,16 +5762,8 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="14" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>LEON TICONA, MARIA FERNANDA</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="14" t="n"/>
       <c r="F28" s="3" t="n"/>
@@ -6390,16 +5774,8 @@
       <c r="A29" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>TITO LAURA, NANCY FIORELLA</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>13:00-22:00</t>
-        </is>
-      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="14" t="n">
         <v>13</v>
@@ -6582,12 +5958,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MARTINEZ PAZ, ROCIO ESPERANZA</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>09:00-18:00</t>
+          <t>09:00-13:30</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6602,12 +5978,12 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>SALVATIERRA PAREJA, MARCO ANTONIO</t>
+          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>19:00-22:45</t>
+          <t>15:30-20:00</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
@@ -6622,32 +5998,40 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>LOPEZ SANCHEZ, NELLY ANDREA</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-15:45</t>
+          <t>09:15-18:15</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>18:15-22:45</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>RAMOS FARFAN, BRYAN  ENRIQUE</t>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>15:45-19:30</t>
+          <t>18:15-15:15</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -6660,8 +6044,16 @@
       <c r="A48" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>18:15-22:45</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="14" t="n">
         <v>23</v>
@@ -6726,12 +6118,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HUANUCO VICUÑA, ABIGAIL LUZ</t>
+          <t>RAMIREZ COTERA, PILAR SINTYA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
@@ -6740,8 +6132,16 @@
           <t>25-30</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>ZUNIGA ANDRADE, JUAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>18:00-22:30</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
@@ -6752,12 +6152,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MACHCO HUARCA, NICOLAS AXEL</t>
+          <t>QUISPE VERA, STEFANI XIOMARA</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:00-15:30</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -6778,12 +6178,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>ZARATE ALAGON, FEDERICO ALEXANDER</t>
+          <t>ALVITES MOZOMBITE, DANIEL ANDRES</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>15:00-19:30</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>
@@ -6844,7 +6244,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>DOMINGO 9 DE MARZO 2025</t>
+          <t>DOMINGO 26 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -6905,12 +6305,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>BARRIENTOS JERI, MILAGROS NICOL</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>06:30-14:00</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -6927,12 +6327,12 @@
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>TITO LAURA, NANCY FIORELLA</t>
+          <t>(T) URBANO ARCOS, FLOR DELIZ</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>13:45-22:45</t>
+          <t>15:45-22:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -6943,8 +6343,16 @@
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="9" t="n"/>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>(T) CHACALTANA NINATAYPE, YENNIFER</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>21:45-22:45</t>
+        </is>
+      </c>
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -6957,12 +6365,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>JIMENEZ VERGARA, ADRIAN MARCELO</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>08:15-12:00</t>
+          <t>09:00-18:00</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -6977,12 +6385,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ROA ZARATE, ELIZABETH LUCY</t>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>12:15-21:15</t>
+          <t>18:15-21:45</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -6997,12 +6405,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CUSI QUISPE, ANDREA ESTEFANY</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:45-12:30</t>
+          <t>09:00-13:30</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -7017,12 +6425,12 @@
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>LOPEZ SANCHEZ, NELLY ANDREA</t>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>13:00-22:00</t>
+          <t>14:45-19:15</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -7037,32 +6445,40 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>QUIQUIA RICALDE, LILIA MARIA</t>
+          <t>ALMENDRE ALMENDRE, KATHERINE</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>09:30-18:30</t>
+          <t>10:15-14:45</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>17:15-21:45</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>VILCAPOMA CHILIN, JULISSA JAZMIN</t>
+          <t>URBANO ARCOS, FLOR DELIZ</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>18:30-22:15</t>
+          <t>15:00-15:45</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -7077,40 +6493,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CASAPAICO RIVERA, ENZO MANUEL</t>
+          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>09:30-13:15</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>RAMOS FARFAN, BRYAN  ENRIQUE</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SICHA JORGE, JOSE ANGELO</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>14:15-18:00</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -7125,40 +6533,32 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>RAMOS TINOCO, JORDAN JAVIER</t>
+          <t>HUAMANI PONCE, ELVIS BENITO</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>09:45-13:30</t>
+          <t>11:15-14:45</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>ALARCON SANDOVAL, ADRIANA FERNANDA</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>LEON TICONA, MARIA FERNANDA</t>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>15:00-18:45</t>
+          <t>17:45-22:15</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -7173,42 +6573,26 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>ROMERO HANARI, VENUS ANUSKA</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>10:00-13:45</t>
+          <t>11:30-20:30</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>LA ROSA EUSEBIO, SHADIA SHAMIRA</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="14" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>ILDEFONSO MOTTA, JHOSSEP ANGELO</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>15:15-19:00</t>
-        </is>
-      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -7221,42 +6605,26 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>YANQUI BRAVO, MIRIAN LUZ</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>13:00-22:00</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>BONILLA SANCHEZ, RAUL FERNANDO</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>19:00-22:45</t>
-        </is>
-      </c>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="14" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>IDME GOMEZ, MILAGROS</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>15:15-19:00</t>
-        </is>
-      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -7269,12 +6637,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>BRANCACHO RAMIREZ, BRINDY</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>11:00-14:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -7287,16 +6655,8 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="14" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ZAPATA VILLANUEVA, FIORELLA YASMIN</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>17:15-21:00</t>
-        </is>
-      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -7309,12 +6669,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ROMERO HAÑARI, VENUS ANUSKA</t>
+          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>11:15-20:15</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
@@ -7341,12 +6701,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>HUAMANI HUAMAN, MARICRUZ DESIDE</t>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>11:30-15:15</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D25" s="3" t="n"/>
@@ -7359,16 +6719,8 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="14" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>FABIAN VALDIVIA, LINDSAY ZIYI</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="14" t="n"/>
       <c r="F26" s="3" t="n"/>
@@ -7379,16 +6731,8 @@
       <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>MAYTA QUINTANA, ANDY KEVIN</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>18:00-21:45</t>
-        </is>
-      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="14" t="n">
         <v>12</v>
@@ -7411,16 +6755,8 @@
       <c r="A29" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>POVEA CANTARO, FARID YASSER</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:00</t>
-        </is>
-      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="14" t="n">
         <v>13</v>
@@ -7603,54 +6939,38 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>ALVITE CORNEJO, ANGIE LUCERO</t>
+          <t>NAVARRO CASTILLO, LIZ MARIELA</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-15:15</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>HUAMANI LOPEZ, DREYDI BELINDA</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>14:45-18:30</t>
-        </is>
-      </c>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>SOTO VELAZCO, EMIR ALESSANDRO</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>16:30-21:00</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="14" t="n"/>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>SALVATIERRA PAREJA, MARCO ANTONIO</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>18:30-22:15</t>
-        </is>
-      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
       <c r="H45" s="3" t="n"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
@@ -7659,40 +6979,32 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>QUISPE MONDRAGON, JUAN ALFONSO</t>
+          <t>CARBAJAL AGUIRRE, ANGELI ESTRELLA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>08:00-11:45</t>
+          <t>07:00-15:15</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>MUÑOZ SOTOMAYOR, MIRIAN RAQUEL</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>16:15-20:00</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SUICA GOÑAS, KEISY YVONNE</t>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>12:00-15:45</t>
+          <t>17:00-21:30</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -7707,12 +7019,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>ALARCON SANDOVAL, ADRIANA FERNANDA</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>19:00-22:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D48" s="3" t="n"/>
@@ -7779,12 +7091,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HUANUCO VICUÑA, ABIGAIL LUZ</t>
+          <t>RAMIREZ COTERA, PILAR SINTYA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>07:00-10:45</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D53" s="3" t="n"/>
@@ -7795,12 +7107,12 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>ZARATE ALAGON, FEDERICO ALEXANDER</t>
+          <t>ZUNIGA ANDRADE, JUAN ANTONIO</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>18:15-22:00</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="H53" s="8" t="n"/>
@@ -7813,12 +7125,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>MACHCO HUARCA, NICOLAS AXEL</t>
+          <t>QUISPE VERA, STEFANI XIOMARA</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>10:45-14:30</t>
+          <t>11:00-15:30</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -7839,12 +7151,12 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CARHUANCHO RAYMUNDO, JAMES JESUS</t>
+          <t>ALVITES MOZOMBITE, DANIEL ANDRES</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>14:30-18:15</t>
+          <t>15:00-19:30</t>
         </is>
       </c>
       <c r="D55" s="3" t="n"/>

--- a/PlantillaSemanal_Exportada.xlsx
+++ b/PlantillaSemanal_Exportada.xlsx
@@ -614,7 +614,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>LUNES 20 DE ABRIL 2026</t>
+          <t>LUNES 27 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -675,12 +675,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>07:00-16:00</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -697,12 +697,12 @@
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>(T) HUAMANI PONCE, ELVIS BENITO</t>
+          <t>(T) SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>15:45-22:00</t>
+          <t>11:15-15:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -715,12 +715,12 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) CHACALTANA NINATAYPE, YENNIFER</t>
+          <t>(T) PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>21:45-22:45</t>
+          <t>14:45-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -775,20 +775,28 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SUICA GONAS, KEISY YVONNE</t>
+          <t>ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>08:30-13:00</t>
+          <t>09:00-13:30</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>16:15-20:45</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
@@ -800,7 +808,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>13:00-22:00</t>
+          <t>13:45-14:45</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -815,12 +823,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>09:45-14:15</t>
+          <t>09:30-14:00</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -835,12 +843,12 @@
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>16:00-20:30</t>
+          <t>16:30-21:00</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -860,7 +868,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10:00-14:30</t>
+          <t>10:30-11:15</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
@@ -875,12 +883,12 @@
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>CORAHUA MEJIA, RENZO JESUS</t>
+          <t>HUAMANI PONCE, ELVIS BENITO</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>17:00-21:30</t>
+          <t>11:30-20:30</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -895,12 +903,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>HUAMANI PONCE, ELVIS BENITO</t>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>13:00-15:45</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -913,16 +921,8 @@
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>17:00-21:30</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>17:15-21:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -967,12 +967,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>CHACALTANA NINATAYPE, YENNIFER</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>18:15-21:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -997,16 +997,8 @@
       <c r="A21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>BENAVIDES PEZO, JAIME EMILIO</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="14" t="n">
         <v>9</v>
@@ -1029,16 +1021,8 @@
       <c r="A23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -1325,40 +1309,32 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-11:30</t>
+          <t>07:30-12:00</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>16:00-20:30</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CHAVEZ CHERO, DANA JHEFEL</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>11:30-16:00</t>
+          <t>12:00-21:00</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -1373,7 +1349,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>BENAVIDES PEZO, JAIME EMILIO</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1459,8 +1435,16 @@
           <t>25-30</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>SLEF, INES</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>18:30-23:00</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
@@ -1497,7 +1481,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>SELF, ERIKA</t>
+          <t>SELF, LIZBET</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -1563,7 +1547,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>MARTES 21 DE ABRIL 2026</t>
+          <t>MARTES 28 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -1624,12 +1608,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>07:00-16:00</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -1646,12 +1630,12 @@
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>(T) JANAMPA CIRIACO, GIAN BRAYAN</t>
+          <t>(T) ALMENDRE ALMENDRE, KATHERINE</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>15:45-20:00</t>
+          <t>11:15-15:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -1669,7 +1653,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>19:45-22:45</t>
+          <t>14:45-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -1684,7 +1668,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1709,7 +1693,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>12:15-21:15</t>
+          <t>13:00-22:00</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -1724,12 +1708,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AYLLON CONSA, DAYANNA DAYSI</t>
+          <t>TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>09:30-18:30</t>
+          <t>09:30-14:00</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -1742,8 +1726,16 @@
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>17:00-21:30</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -1756,7 +1748,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>SUICA GONAS, KEISY YVONNE</t>
+          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1768,28 +1760,20 @@
       <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>17:00-21:30</t>
-        </is>
-      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>15:30-15:45</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -1804,12 +1788,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
+          <t>ALMENDRE ALMENDRE, KATHERINE</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10:30-15:00</t>
+          <t>10:30-11:15</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
@@ -1824,12 +1808,12 @@
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>17:30-22:00</t>
+          <t>11:30-20:30</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -1849,7 +1833,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>13:45-19:45</t>
+          <t>13:45-14:45</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -1862,8 +1846,16 @@
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>17:45-22:15</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -1876,12 +1868,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>SULLON MANDUJANO, GREYS NICOLE</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>17:45-22:15</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -1906,16 +1898,8 @@
       <c r="A19" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>18:00-22:30</t>
-        </is>
-      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="14" t="n">
         <v>8</v>
@@ -1938,16 +1922,8 @@
       <c r="A21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="14" t="n">
         <v>9</v>
@@ -2246,7 +2222,7 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>BENAVIDES PEZO, JAIME EMILIO</t>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2266,40 +2242,32 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-11:30</t>
+          <t>07:30-16:30</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>CHACALTANA NINATAYPE, YENNIFER</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>16:00-20:30</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CHAVEZ CHERO, DANA JHEFEL</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>11:30-16:00</t>
+          <t>16:30-21:00</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -2438,7 +2406,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>SELF, ERIKA</t>
+          <t>SELF, LIZBET</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -2504,7 +2472,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>MIÉRCOLES 22 DE ABRIL 2026</t>
+          <t>MIÉRCOLES 29 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -2565,12 +2533,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>07:00-16:00</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -2587,12 +2555,12 @@
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>(T) ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
+          <t>(T) ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>15:45-18:30</t>
+          <t>11:15-15:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -2610,7 +2578,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>18:15-22:45</t>
+          <t>14:45-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -2625,40 +2593,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ENERO BARZOLA, ENRIQUE HANS</t>
+          <t>TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>08:00-12:30</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>13:45-18:15</t>
+          <t>13:30-22:30</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -2673,12 +2633,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>10:00-19:00</t>
+          <t>09:30-14:00</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -2691,8 +2651,16 @@
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>15:30-20:00</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -2725,12 +2693,12 @@
       <c r="A12" s="14" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CORAHUA MEJIA, RENZO JESUS</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>16:00-20:30</t>
+          <t>17:00-21:30</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -2745,7 +2713,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>SUICA GONAS, KEISY YVONNE</t>
+          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2765,7 +2733,7 @@
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SULLON MANDUJANO, GREYS NICOLE</t>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2785,12 +2753,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>10:30-15:00</t>
+          <t>10:30-11:15</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -2805,12 +2773,12 @@
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>17:30-22:00</t>
+          <t>11:30-20:30</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -2825,12 +2793,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>14:00-15:45</t>
+          <t>13:45-14:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -2845,12 +2813,12 @@
       <c r="A18" s="14" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>18:00-22:30</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
@@ -2863,16 +2831,8 @@
       <c r="A19" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>BENAVIDES PEZO, JAIME EMILIO</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>18:00-22:30</t>
-        </is>
-      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="14" t="n">
         <v>8</v>
@@ -3195,7 +3155,7 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3215,12 +3175,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-11:30</t>
+          <t>07:30-16:30</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
@@ -3235,12 +3195,12 @@
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AYLLON CONSA, DAYANNA DAYSI</t>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>13:30-22:30</t>
+          <t>16:30-21:00</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -3379,7 +3339,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>SELF, ERIKA</t>
+          <t>SELF, LIZBET</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3445,7 +3405,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>JUEVES 23 DE ABRIL 2026</t>
+          <t>JUEVES 30 DE ABRIL 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -3506,12 +3466,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>07:00-16:00</t>
+          <t>01:00-10:00</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -3528,12 +3488,12 @@
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>CHACALTANA NINATAYPE, YENNIFER</t>
+          <t>(T) TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>15:45-20:15</t>
+          <t>09:45-14:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -3546,12 +3506,12 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) LLACCHO MENESES, KATHERIN STEFANIA</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>20:00-22:45</t>
+          <t>13:45-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -3566,12 +3526,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>07:45-12:15</t>
+          <t>07:30-16:30</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -3586,12 +3546,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>AYLLON CONSA, DAYANNA DAYSI</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>13:00-22:00</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -3606,12 +3566,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TARDILLO COPA, YOVANNA MELISSA</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>09:45-14:15</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -3626,12 +3586,12 @@
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>BENAVIDES PEZO, JAIME EMILIO</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>17:30-22:00</t>
+          <t>13:45-22:45</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -3646,26 +3606,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
+          <t>TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10:00-19:00</t>
+          <t>09:30-09:45</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>17:30-22:00</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ALMENDRE ALMENDRE, KATHERINE</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>10:00-14:30</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -3678,7 +3654,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ALMENDRE ALMENDRE, KATHERINE</t>
+          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3698,12 +3674,12 @@
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>18:15-22:45</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -3718,12 +3694,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>13:45-20:00</t>
+          <t>10:00-14:30</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -3736,8 +3712,16 @@
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>18:00-22:30</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -4089,7 +4073,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>09:00-18:00</t>
+          <t>10:00-19:00</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -4102,16 +4086,8 @@
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="14" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>SULLON MANDUJANO, GREYS NICOLE</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="14" t="n"/>
       <c r="F45" s="3" t="n"/>
@@ -4138,12 +4114,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>17:00-21:30</t>
+          <t>17:15-21:45</t>
         </is>
       </c>
       <c r="H46" s="3" t="n"/>
@@ -4170,8 +4146,16 @@
       <c r="A48" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>13:45-22:45</t>
+        </is>
+      </c>
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="14" t="n">
         <v>23</v>
@@ -4362,7 +4346,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>VIERNES 24 DE ABRIL 2026</t>
+          <t>VIERNES 1 DE MAYO 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -4423,7 +4407,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>ENERO BARZOLA, ENRIQUE HANS</t>
+          <t>TARDILLO COPA, YOVANNA MELISSA</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -4437,38 +4421,54 @@
           <t>1 PREF</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="8" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>17:15-21:45</t>
+        </is>
+      </c>
       <c r="H4" s="8" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
+          <t>(T) ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>11:15-20:15</t>
+          <t>11:15-14:30</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>(T) ROMERO HANARI, VENUS ANUSKA</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>21:30-22:45</t>
+        </is>
+      </c>
       <c r="H5" s="12" t="n"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) LLACCHO MENESES, KATHERIN STEFANIA</t>
+          <t>(T) NAVARRO CASTILLO, LIZ MARIELA</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>20:00-22:45</t>
+          <t>14:15-17:30</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CARBAJAL AGUIRRE, ANGELI ESTRELLA</t>
+          <t>ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>07:00-16:00</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -4503,12 +4503,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>BENAVIDES PEZO, JAIME EMILIO</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>18:00-22:30</t>
+          <t>13:00-22:00</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -4528,27 +4528,35 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>07:45-12:15</t>
+          <t>09:30-14:00</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CHACALTANA NINATAYPE, YENNIFER</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>15:00-19:30</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>URBANO ARCOS, FLOR DELIZ</t>
+          <t>NAVARRO CASTILLO, LIZ MARIELA</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>12:15-21:00</t>
+          <t>14:00-14:15</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -4563,12 +4571,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>HUAMANI PONCE, ELVIS BENITO</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>09:30-18:30</t>
+          <t>10:00-19:00</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -4581,16 +4589,8 @@
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ROMERO HANARI, VENUS ANUSKA</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>18:30-22:15</t>
-        </is>
-      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>HUARACA HUAMAN, DIEGO ADRIEL</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10:00-14:00</t>
+          <t>10:00-11:15</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
@@ -4623,12 +4623,12 @@
       <c r="A14" s="14" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
+          <t>URBANO ARCOS, FLOR DELIZ</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>18:15-22:45</t>
+          <t>12:00-21:00</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ALMENDRE ALMENDRE, KATHERINE</t>
+          <t>ROMERO HANARI, VENUS ANUSKA</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>10:15-14:45</t>
+          <t>18:00-21:30</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -4661,16 +4661,8 @@
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="14" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>CHAVEZ CHERO, DANA JHEFEL</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -4683,12 +4675,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
+          <t>CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>13:00-22:00</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -4713,16 +4705,8 @@
       <c r="A19" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>13:45-20:00</t>
-        </is>
-      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="14" t="n">
         <v>8</v>
@@ -5045,7 +5029,7 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5065,7 +5049,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>NAVARRO CASTILLO, LIZ MARIELA</t>
+          <t>CARBAJAL AGUIRRE, ANGELI ESTRELLA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5090,7 +5074,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>18:00-22:30</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -5169,7 +5153,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>ALVITES MOZOMBITE, DANIEL ANDRES</t>
+          <t>QUISPE VERA, STEFANI XIOMARA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -5203,12 +5187,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>QUISPE VERA, STEFANI XIOMARA</t>
+          <t>ALVITES MOZOMBITE, DANIEL ANDRES</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>11:30-16:00</t>
+          <t>11:00-15:30</t>
         </is>
       </c>
       <c r="D54" s="3" t="n"/>
@@ -5229,7 +5213,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>SELF, ERIKA</t>
+          <t>SELF, MELISSA</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -5295,7 +5279,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>SÁBADO 25 DE ABRIL 2026</t>
+          <t>SÁBADO 2 DE MAYO 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -5356,12 +5340,12 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>ENERO BARZOLA, ENRIQUE HANS</t>
+          <t>ESPINOZA YIP, MANUEL ENRIQUE</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>07:45-12:15</t>
+          <t>07:00-16:00</t>
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
@@ -5378,12 +5362,12 @@
       <c r="A5" s="11" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>(T) CHAVEZ CHERO, DANA JHEFEL</t>
+          <t>(T) AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>12:00-15:30</t>
+          <t>15:45-21:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -5396,12 +5380,12 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) ALCOCER GAMBOA, SERGIO FABRIZIO</t>
+          <t>(T) MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>15:15-22:45</t>
+          <t>20:45-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -5416,12 +5400,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ROCA IBARAN, MIRLA VALENTINA</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>09:30-14:00</t>
+          <t>09:15-18:15</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -5436,12 +5420,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>URBANO ARCOS, FLOR DELIZ</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>15:45-22:30</t>
+          <t>18:15-20:45</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -5456,12 +5440,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
+          <t>SUICA GONAS, KEISY YVONNE</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>10:00-19:00</t>
+          <t>09:45-14:15</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -5474,8 +5458,16 @@
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="14" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>CARBAJAL AGUIRRE, ANGELI ESTRELLA</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>17:15-20:45</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="3" t="n"/>
@@ -5488,12 +5480,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>SILVA MALPARTIDA, ALDAID ELIO</t>
+          <t>PAREDES BENDEZU, SILVANA ANDREI</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10:30-15:00</t>
+          <t>10:00-19:00</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -5506,16 +5498,8 @@
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="14" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>CHACALTANA NINATAYPE, YENNIFER</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>16:15-20:45</t>
-        </is>
-      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -5528,12 +5512,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ROMERO HANARI, VENUS ANUSKA</t>
+          <t>ALMENDRE ALMENDRE, KATHERINE</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10:30-19:15</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
@@ -5546,8 +5530,16 @@
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="14" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>17:30-22:00</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -5560,12 +5552,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CHAVEZ CHERO, DANA JHEFEL</t>
+          <t>HUAMANI PONCE, ELVIS BENITO</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>11:00-12:00</t>
+          <t>10:30-18:15</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -5580,12 +5572,12 @@
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>AYLLON CONSA, DAYANNA DAYSI</t>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>12:45-21:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -5600,12 +5592,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CORAHUA MEJIA, RENZO JESUS</t>
+          <t>ROMERO HANARI, VENUS ANUSKA</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>17:15-21:45</t>
+          <t>11:00-18:45</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -5632,12 +5624,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
+          <t>CHAVEZ CHERO, DANA JHEFEL</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>17:30-22:00</t>
+          <t>11:15-15:45</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -5650,8 +5642,16 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="14" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>18:15-22:45</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -5664,12 +5664,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>18:15-22:45</t>
+          <t>12:00-15:45</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -5694,16 +5694,8 @@
       <c r="A23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -5958,12 +5950,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>SUICA GONAS, KEISY YVONNE</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>09:00-13:30</t>
+          <t>07:45-12:15</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -5978,12 +5970,12 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
+          <t>URBANO ARCOS, FLOR DELIZ</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>15:30-20:00</t>
+          <t>17:00-22:00</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
@@ -5998,40 +5990,32 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
+          <t>NAVARRO CASTILLO, LIZ MARIELA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>09:15-18:15</t>
+          <t>09:00-18:00</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>18:15-15:15</t>
+          <t>18:00-22:30</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -6046,7 +6030,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CHOTA CHAVEZ, ROLANDO PIERO</t>
+          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -6244,7 +6228,7 @@
     <row r="2" ht="19.5" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>DOMINGO 26 DE ABRIL 2026</t>
+          <t>DOMINGO 3 DE MAYO 2026</t>
         </is>
       </c>
       <c r="B2" s="16" t="n"/>
@@ -6332,7 +6316,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>15:45-22:00</t>
+          <t>15:45-22:30</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -6345,12 +6329,12 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>(T) CHACALTANA NINATAYPE, YENNIFER</t>
+          <t>(T) AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>21:45-22:45</t>
+          <t>22:15-22:45</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -6365,7 +6349,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
+          <t>NAVARRO CASTILLO, LIZ MARIELA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6385,12 +6369,12 @@
       <c r="A8" s="14" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>CHACALTANA NINATAYPE, YENNIFER</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>18:15-21:45</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -6405,12 +6389,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
+          <t>LLACCHO MENESES, KATHERIN STEFANIA</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>09:00-13:30</t>
+          <t>09:15-18:15</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -6425,12 +6409,12 @@
       <c r="A10" s="14" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
+          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>14:45-19:15</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
@@ -6450,7 +6434,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>10:15-14:45</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
@@ -6459,12 +6443,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>CORAHUA MEJIA, RENZO JESUS</t>
+          <t>SULLON MANDUJANO, GREYS NICOLE</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>17:15-21:45</t>
+          <t>17:30-22:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="n"/>
@@ -6533,12 +6517,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>HUAMANI PONCE, ELVIS BENITO</t>
+          <t>ENERO BARZOLA, ENRIQUE HANS</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>11:15-14:45</t>
+          <t>10:30-15:00</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -6553,12 +6537,12 @@
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ALCOCER GAMBOA, SERGIO FABRIZIO</t>
+          <t>QUINTO MEDRANO, MERLY JAZMIN</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>17:45-22:15</t>
+          <t>18:15-22:45</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -6573,12 +6557,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ROMERO HANARI, VENUS ANUSKA</t>
+          <t>CARBAJAL AGUIRRE, ANGELI ESTRELLA</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>11:30-20:30</t>
+          <t>11:00-20:00</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -6605,12 +6589,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>AYLLON CONSA, DAYANNA DAYSI</t>
+          <t>ROMERO HANARI, VENUS ANUSKA</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>13:00-22:00</t>
+          <t>11:15-20:15</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -6635,16 +6619,8 @@
       <c r="A21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="14" t="n">
         <v>9</v>
@@ -6667,16 +6643,8 @@
       <c r="A23" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>JANAMPA CIRIACO, GIAN BRAYAN</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -6699,16 +6667,8 @@
       <c r="A25" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>CASAFRANCA QUISPE, LEONARDO AXEL</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>18:15-22:45</t>
-        </is>
-      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="14" t="n">
         <v>11</v>
@@ -6939,32 +6899,40 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>NAVARRO CASTILLO, LIZ MARIELA</t>
+          <t>VEREAU SOLANO, ANTONIO FAUSTO</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>07:00-15:15</t>
+          <t>07:00-11:30</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>CORAHUA MEJIA, RENZO JESUS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>17:15-21:45</t>
+        </is>
+      </c>
       <c r="H44" s="3" t="n"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
+          <t>HUAMANI PONCE, ELVIS BENITO</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>16:30-21:00</t>
+          <t>11:30-16:15</t>
         </is>
       </c>
       <c r="D45" s="3" t="n"/>
@@ -6979,12 +6947,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CARBAJAL AGUIRRE, ANGELI ESTRELLA</t>
+          <t>ROCA IBARAN, MIRLA VALENTINA</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>07:00-15:15</t>
+          <t>08:00-12:30</t>
         </is>
       </c>
       <c r="D46" s="3" t="n"/>
@@ -6999,12 +6967,12 @@
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SULLON MANDUJANO, GREYS NICOLE</t>
+          <t>AYLLON CONSA, DAYANNA DAYSI</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>17:00-21:30</t>
+          <t>13:45-22:15</t>
         </is>
       </c>
       <c r="D47" s="3" t="n"/>
@@ -7019,7 +6987,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>ANCAJIMA SANCHEZ, SALOME NAJHELY</t>
+          <t>MENDIETA ROJAS, KIOMI XIOMARA</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7091,7 +7059,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>RAMIREZ COTERA, PILAR SINTYA</t>
+          <t>QUISPE VERA, STEFANI XIOMARA</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -7125,7 +7093,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>QUISPE VERA, STEFANI XIOMARA</t>
+          <t>RAMIREZ COTERA, PILAR SINTYA</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
